--- a/new/260718.xlsx
+++ b/new/260718.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tac3\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE6F221-BCEE-4720-A6BA-9BEAD47D23C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744BAB3F-7D44-4439-86F5-2C543FEFC13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16150" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8600" yWindow="2380" windowWidth="16150" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>每周采访-160717-Christian</t>
   </si>
@@ -508,6 +509,16 @@
 dass ihre eigenen Kinder keinen festen Arbeitsplatz mehr bekommen oder dass man 40 Jahre arbeitet und am Ende eine Rente hat, 
 die kleiner ist, mehr Vertrauen darin existiert, dass sich Leistung lohnt, 
 dass Menschen in sozial schwierigen Lagen Hilfe bekommen, dass der Staat .</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"aber nicht bei Dingen, die Sie und ich selber in der Hand behalten können, wofür wir überhaupt keine Politik, erst recht keine europäische Politik brauchen.
+Remme: Ich habe den Namen Genscher erwähnt.
+Diese Generation wird gefeiert für ihre Gründung der Europäischen Union.
+Muss man ehrlicherweise auch sagen, dass viele Geburtsfehler durch diese Generation angelegt waren, die uns jetzt Kopfzerbrechen machen?
+eine der größten Errungenschaften des vergangenen Jahrhunderts überhaupt.
+Denn da drückt sich ja nicht nur wirtschaftliche Aktivität aus, sondern das ist eben der Verzicht auf Grenzen.
+Die Fehler werden jetzt gemacht, wenn schon wieder zum Beispiel beim europäischen Stabilitätspakt Regeln gebrochen und verwässert werden, mehr Schulden gemacht werden dürfen und die deutsche Bundesregierung nicht als Wächter dieser Vertragsbestimmungen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -870,6 +881,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61289ED6-4026-4582-8582-D01CC58924EC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="364" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>

--- a/new/260718.xlsx
+++ b/new/260718.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744BAB3F-7D44-4439-86F5-2C543FEFC13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88270C11-222C-4636-8881-B161E12A26C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8600" yWindow="2380" windowWidth="16150" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8600" yWindow="2380" windowWidth="16150" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>每周采访-160717-Christian</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -44,126 +42,6 @@
   </si>
   <si>
     <t>每周采访-160828-Frod</t>
-  </si>
-  <si>
-    <t>aber nicht bei Dingen, die Sie und ich selber in der Hand behalten können, wofür wir überhaupt keine Politik, erst recht keine europäische Politik brauchen.
-Remme: Ich habe den Namen Genscher erwähnt.
-Diese Generation wird gefeiert für ihre Gründung der Europäischen Union.
-Muss man ehrlicherweise auch sagen, dass viele Geburtsfehler durch diese Generation angelegt waren, die uns jetzt Kopfzerbrechen machen?
-Lindner: Ich sehe eher in den vergangenen Jahren die Defizite, die sich jetzt auch beschleunigen, nicht bei der Gründungsgeneration.
-Also der Binnenmarkt von 1992, Herr Remme, das halte ich für eine der größten Errungenschaften des vergangenen Jahrhunderts überhaupt.
-Denn da drückt sich ja nicht nur wirtschaftliche Aktivität aus, sondern das ist eben der Verzicht auf Grenzen.
-Die Fehler werden jetzt gemacht, wenn schon wieder zum Beispiel beim europäischen Stabilitätspakt Regeln gebrochen und verwässert werden, mehr Schulden gemacht werden dürfen und die deutsche Bundesregierung nicht als Wächter dieser Vertragsbestimmungen auftritt, sondern in Gestalt von Herrn Gabriel noch ermuntert dazu, mehr Schulden zu machen.
-Remme: Kurze Frage zum Schluss noch.
-Wir haben gesprochen über Türkei, über Terror, über Brexit.
-Ist eines dieser drei Themen wahlentscheidend im nächsten Jahr?
-Lindner: Der Zustand Europas und die deutsche Rolle, das wird natürlich eine Diskussion im Bundestagswahlkampf sein.
-Unsere Haltung ist klar.
-Wir wollen Europa, aber Europa muss besser werden und in seinem Zentrum muss der Gedanke der Freiheit und nicht der des Bürokratismus stehen.
-Remme: Vielen Dank für das Gespräch heute.
-Lindner: Gerne, Herr Remme</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Frank: Ja.
-Zunächst möchte ich vielleicht eines vorweg sagen.
-Flüchtlinge stehen bei uns nicht unter einem Generalverdacht.
-Es ist auch für uns nicht entscheidend, ob jemand Flüchtling ist oder einen anderen Aufenthaltstitel hat.
-Es ist für uns auch nicht entscheidend, welcher Nationalität jemand angehört.
-Für uns ist entscheidend: Radikalisiert sich jemand und ist jemand bereit Anschläge zu begehen oder sich einer terroristischen Vereinigung anzuschließen?
-Wir haben in den letzten Monaten – nicht nur wir, sondern auch vor allem die Polizeibehörden und die Sicherheitsbehörden – vermehrt Hinweise darauf bekommen, dass sich auch bei den Flüchtlingen Angehörige terroristischer Organisationen befunden haben sollen.
-Wir gehen diesen Hinweisen im Einzelnen nach.
-Da gibt es eine Reihe von Hinweisen, die sich als nichtzutreffend herausgestellt haben.
-Aber immer dann, wenn sich der Verdacht ergibt, ein begründeter Verdacht ergibt, dass sich nicht nur unter Flüchtlingen Angehörige des sogenannten Islamischen Staates oder anderer terroristischer Vereinigungen, der Al-Kaida befinden, dann greifen wir diese Verfahren auf und versuchen, dort die Täter oder die Beschuldigten zu überführen.
-Geuther: Trotzdem noch mal: Wie gehen Sie mit diesen tatsächlichen Schwierigkeiten um?
-Frank: Natürlich ist es für uns immer wieder schwierig, in einem doch fernab gelegenen Kriegsgebiet – in dem ja jegliche staatliche Kontrolle, jede jegliche staatliche Struktur zusammengebrochen ist – auch Beweise zu erheben.
-Allerdings sind wir nicht immer darauf angewiesen im Wege der Rechtshilfe Beweise aus diesem syrisch-irakischen Kriegsgebiet zu gewinnen.
-Wir haben auch sehr viele Beweismittel hier in Deutschland.
-Allein mit dem Flüchtlingsstrom sind auch sehr viele geschädigte, geschundene Personen, vertriebene Personen, die Opfer des sogenannten Islamischen Staates geworden sind, hierher nach Deutschland gekommen.
-Auch insoweit stehen uns sehr viele Beweismittel als Zeugen zur Verfügung.
-Geuther: Und nur, um das noch mal klarzustellen, ich hatte die Frage jetzt eingeleitet über die Flüchtlinge, aber von den mehr als 130 Verfahren, die Sie führen, ist das natürlich nur der allergeringste Teil.
-Wir haben ja bisher im Zusammenhang mit Syrien vor allem über die verschiedenen islamistischen Organisationen gesprochen.
-Der syrische Menschenrechtsanwalt Ibrahim Alkasem hat vor Kurzem in der Online-Ausgabe der """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Zeit"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" an Sie appelliert, systematisch und strukturiert auch insbesondere Folter durch die Assad-Seite in den Blick zu nehmen.
-Frank: Wir haben nicht nur terroristische Organisationen im Blick.
-Die Bundesanwaltschaft ist seit dem Inkrafttreten des Rom-Statuts ja mit der Umsetzung und mit der Verfolgung von Straftaten nach dem Völkerstrafgesetzbuch – das zeitgleich in Kraft getreten ist – beauftragt.
-Wir führen – was den syrisch-irakischen Bürgerkrieg anbelangt, mehrere Strukturverfahren, um zu beobachten und herauszufinden und zu ermitteln und Beweise zu sichern: Wer könnte Kriegsverbrechen begehen, Verbrechen gegen die Menschlichkeit?
-Wir haben da sowohl den sogenannten Islamischen Staat im Blick, wir haben da aber auch das Regime im Blick.
-Und insoweit ist es für uns auch wichtig, Beweise, Beweismittel – das sind in der Regel Zeugen, die als Flüchtlinge hierher nach Deutschland gekommen sind –, diese Beweismittel zu sichten, auch in Kooperation mit anderen ausländischen Staaten.
-Denn Flüchtlinge sind ja nicht nur nach Deutschland gekommen.
-Insoweit stehen wir in einem engen Austausch mit anderen Staatsanwaltschaften anderer europäischer Länder, in denen auch entsprechende War Crime Units gebildet wurden, um hier gemeinsam Beweise zu sichern, die wir vielleicht einmal nutzbar machen können, wenn Teilnehmer solcher Kriegsverbrecherhandlungen hierher nach Deutschland kommen.
-Geuther: Sie hören das Interview der Woche im Deutschlandfunk mit Generalbundesanwalt Peter Frank.
-Herr Frank, noch vor einigen Wochen hätten wir dieses Gespräch wahrscheinlich mit dem Schwerpunkt Rechtsextremismus begonnen.
-Sie haben mehrere Verfahren übernommen.
-Im April haben Sie fünf Personen festnehmen lassen wegen des Verdachts der Mitgliedschaft in einer rechtsterroristischen Vereinigung.
-Dieser """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gruppe Freital"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" rechnen Sie auch noch weitere Personen hinzu.
-Hätten Sie sich ohne die Erfahrung mit dem NSU vorstellen können, dass es Terrorismus von rechts in Deutschland geben könnte?
-Frank: Durch die Erkenntnisse aus dem NSU-Komplex hat sich der Blickwinkel auf den Themenkomplex Rechtsextremismus sicherlich noch etwas stärker verstärkt.
-Die Bundesanwaltschaft hat in dieser Folge ein eigenes Referat """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Deutscher Terrorismus rechts"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" gebildet.
-Wir haben in Zusammenarbeit auch mit den Länderbehörden in der Zwischenzeit eine Strategie entwickelt, wie wir das Thema Rechtsterrorismus, Rechtsextremismus auch aus Sicht der Strafverfolgungsbehörden stärker durchleuchten und beleuchten wollen.
-Denn eines muss klar sein: Eine terroristische Organisation wie der NSU, der doch über Jahre hinweg vielleicht unbekannt und unerkannt in Deutschland Morde begangen hat, das darf es nicht mehr geben.
-Und insoweit sind wir in einem engen Austausch und in einer engen Vernetzung, nicht nur mit den Staatsanwaltschaften der Länder, sondern auch mit den Polizeibehörden des Bundes und der Länder, mit den Verfassungsschutzbehörden des Bundes und der Länder.
-Das ist eine gesamtgesellschaftliche Aufgabe.
-Dazu gehört auch, dass der Generalbundesanwalt das eine oder andere Verfahren von den Ländern – das auch dort stärker ermittelt und ausgeleuchtet wird – immer wieder übernimmt.
-Und eine Folge war die Übernahme dieses Verfahrens Freital.
-Geuther: Und gerade da hatte die Aufdeckung der NSU-Taten ja auch tatsächlich Konsequenzen für Ihre Behörde bei der Frage der Übernahme und der Zuständigkeit.
-Dafür muss es ja immer einen besonderen Grund geben, sonst sind die Landesbehörden zuständig.
-Und in der Vergangenheit gab es da auch schon Streit.
-Jetzt müssen die Landesbehörden Sie vor allem früher informieren, wenn es Anhaltspunkte gibt zum Beispiel, ob ein Fall besondere Bedeutung hat.
-Klappt das denn jetzt?
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Recht muss immer durchgesetzt werden"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Frank: Wir stehen in einem sehr engen Austausch.
-Wir haben in den letzten anderthalb Jahren diverse Regionalkonferenzen mit den Staatsanwaltschaften, Polizeibehörden, Verfassungsschutzbehörden der Länder, teilweise unter Beteiligung auch von Behörden aus dem Ausland durchgeführt.
-Denn eines muss man sehen: Auch der Rechtsextremismus ist nicht nur auf Deutschland beschränkt.
-Auch hier gibt es immer wieder Kontakte in das Ausland.
-Sei es allein, was die Beschaffung bestimmter pyrotechnischer Gegenstände anbelangt.
-Sei es als Rückzugsgebiete oder Vernetzung mit anderen ausländischen rechtsterroristischen oder rechtsextremistischen Strukturen.
-Wir haben ein Ansprechpartner-Netzwerk entwickelt.
-Wir versuchen auch, dieses noch weiter zu entwickeln, indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
-Und insoweit berichten uns die Länder sehr frühzeitig.
-Wir berichten den Ländern aufgrund unserer Erkenntnisse.
-Und ich glaube, das ist auch das Entscheidende.
-Geuther: Es wurde einzelnen Ländern – gerade auch im Osten der Republik – vorgeworfen, eine Tat später als rechtsextremistisch einzuordnen als andere – vorsichtig gesagt.
-Stimmt das?
-Und wenn ja, stimmt das immer noch?
-Frank: Um hier eine Sensibilisierung auch bei jedem zu erreichen, haben wir, hat die Bundesanwaltschaft, in Zusammenarbeit aber auch mit den Generalstaatsanwaltschaften der Länder verschiedene Instrumentarien entwickelt.
-Eines ist zum Beispiel – auch, wenn das vielleicht banal klingen mag – die Entwicklung eines Formblattes, wie man frühzeitig rechtsextremistische Straftaten erkennen kann.
-Denn vielfach ist ein erster Kontakt mit rechtsextremistischen Straftaten nicht immer dann gegeben, wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
-Häufig sind es Straftaten der Allgemeinkriminalität.
-Es sind Körperverletzungshandlungen.
-Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
-Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
-Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
-Wie gehen Sie als Generalbundesanwalt damit um?
-Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
-In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
-Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
-Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Jeder versteht, wenn die EU mit bestimmten Ländern auf der Welt Verträge abschließt über Freihandel, dass das überwiegend in deren Interesse ist, weil die auch Vorkehrungen bekommen, die es dann kapitalkräftigen Investoren aus Europa und den USA als ein geordnetes Wagnis erscheinen lassen, dort zu investieren.
@@ -521,12 +399,110 @@
 Die Fehler werden jetzt gemacht, wenn schon wieder zum Beispiel beim europäischen Stabilitätspakt Regeln gebrochen und verwässert werden, mehr Schulden gemacht werden dürfen und die deutsche Bundesregierung nicht als Wächter dieser Vertragsbestimmungen</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Beweise aus diesem syrisch-irakischen Kriegsgebiet zu gewinnen.
+Wir haben auch sehr viele Beweismittel hier in Deutschland.
+Allein mit dem Flüchtlingsstrom sind auch sehr viele geschädigte, geschundene Personen, vertriebene Personen, die Opfer des sogenannten Islamischen Staates geworden sind, hierher nach Deutschland gekommen.
+Auch insoweit stehen uns sehr viele Beweismittel als Zeugen zur Verfügung.
+Geuther: Und nur, um das noch mal klarzustellen, ich hatte die Frage jetzt eingeleitet über die Flüchtlinge, aber von den mehr als 130 Verfahren, die Sie führen, ist das natürlich nur der allergeringste Teil.
+Wir haben ja bisher im Zusammenhang mit Syrien vor allem über die verschiedenen islamistischen Organisationen gesprochen.
+Der syrische Menschenrechtsanwalt Ibrahim Alkasem hat vor Kurzem in der Online-Ausgabe der """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Zeit"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" an Sie appelliert, systematisch und strukturiert auch insbesondere Folter durch die Assad-Seite in den Blick zu nehmen.
+Frank: Wir haben nicht nur terroristische Organisationen im Blick.
+Die Bundesanwaltschaft ist seit dem Inkrafttreten des Rom-Statuts ja mit der Umsetzung und mit der Verfolgung von Straftaten nach dem Völkerstrafgesetzbuch – das zeitgleich in Kraft getreten ist – beauftragt.
+Wir führen – was den syrisch-irakischen Bürgerkrieg anbelangt, mehrere Strukturverfahren, um zu beobachten und herauszufinden und zu ermitteln und Beweise zu sichern: Wer könnte Kriegsverbrechen begehen, Verbrechen gegen die Menschlichkeit?
+Wir haben da sowohl den sogenannten Islamischen Staat im Blick, wir haben da aber auch das Regime im Blick.
+Und insoweit ist es für uns auch wichtig, Beweise, Beweismittel – das sind in der Regel Zeugen, die als Flüchtlinge hierher nach Deutschland gekommen sind –, diese Beweismittel zu sichten, auch in Kooperation mit anderen ausländischen Staaten.
+Denn Flüchtlinge sind ja nicht nur nach Deutschland gekommen.
+Insoweit stehen wir in einem engen Austausch mit anderen Staatsanwaltschaften anderer europäischer Länder, in denen auch entsprechende War Crime Units gebildet wurden, um hier gemeinsam Beweise zu sichern, die wir vielleicht einmal nutzbar machen können, wenn Teilnehmer solcher Kriegsverbrecherhandlungen hierher nach Deutschland kommen.
+Geuther: Sie hören das Interview der Woche im Deutschlandfunk mit Generalbundesanwalt Peter Frank.
+Herr Frank, noch vor einigen Wochen hätten wir dieses Gespräch wahrscheinlich mit dem Schwerpunkt Rechtsextremismus begonnen.
+Sie haben mehrere Verfahren übernommen.
+Im April haben Sie fünf Personen festnehmen lassen wegen des Verdachts der Mitgliedschaft in einer rechtsterroristischen Vereinigung.
+Dieser """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Gruppe Freital"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" rechnen Sie auch noch weitere Personen hinzu.
+Hätten Sie sich ohne die Erfahrung mit dem NSU vorstellen können, dass es Terrorismus von rechts in Deutschland geben könnte?
+Frank: Durch die Erkenntnisse aus dem NSU-Komplex hat sich der Blickwinkel auf den Themenkomplex Rechtsextremismus sicherlich noch etwas stärker verstärkt.
+Die Bundesanwaltschaft hat in dieser Folge ein eigenes Referat """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Deutscher Terrorismus rechts"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" gebildet.
+Wir haben in Zusammenarbeit auch mit den Länderbehörden in der Zwischenzeit eine Strategie entwickelt, wie wir das Thema Rechtsterrorismus, Rechtsextremismus auch aus Sicht der Strafverfolgungsbehörden stärker durchleuchten und beleuchten wollen.
+Denn eines muss klar sein: Eine terroristische Organisation wie der NSU, der doch über Jahre hinweg vielleicht unbekannt und unerkannt in Deutschland Morde begangen hat, das darf es nicht mehr geben.
+Und insoweit sind wir in einem engen Austausch und in einer engen Vernetzung, nicht nur mit den Staatsanwaltschaften der Länder, sondern auch mit den Polizeibehörden des Bundes und der Länder, mit den Verfassungsschutzbehörden des Bundes und der Länder.
+Das ist eine gesamtgesellschaftliche Aufgabe.
+Dazu gehört auch, dass der Generalbundesanwalt das eine oder andere Verfahren von den Ländern – das auch dort stärker ermittelt und ausgeleuchtet wird – immer wieder übernimmt.
+Und eine Folge war die Übernahme dieses Verfahrens Freital.
+Geuther: Und gerade da hatte die Aufdeckung der NSU-Taten ja auch tatsächlich Konsequenzen für Ihre Behörde bei der Frage der Übernahme und der Zuständigkeit.
+Dafür muss es ja immer einen besonderen Grund geben, sonst sind die Landesbehörden zuständig.
+Und in der Vergangenheit gab es da auch schon Streit.
+Jetzt müssen die Landesbehörden Sie vor allem früher informieren, wenn es Anhaltspunkte gibt zum Beispiel, ob ein Fall besondere Bedeutung hat.
+Klappt das denn jetzt?
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Recht muss immer durchgesetzt werden"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Frank: Wir stehen in einem sehr engen Austausch.
+Wir haben in den letzten anderthalb Jahren diverse Regionalkonferenzen mit den Staatsanwaltschaften, Polizeibehörden, Verfassungsschutzbehörden der Länder, teilweise unter Beteiligung auch von Behörden aus dem Ausland durchgeführt.
+Denn eines muss man sehen: Auch der Rechtsextremismus ist nicht nur auf Deutschland beschränkt.
+Auch hier gibt es immer wieder Kontakte in das Ausland.
+Sei es allein, was die Beschaffung bestimmter pyrotechnischer Gegenstände anbelangt.
+Sei es als Rückzugsgebiete oder Vernetzung mit anderen ausländischen rechtsterroristischen oder rechtsextremistischen Strukturen.
+Wir haben ein Ansprechpartner-Netzwerk entwickelt.
+Wir versuchen auch, dieses noch weiter zu entwickeln, indem wir die Länderstaatsanwaltschaften noch enger an uns heranbinden.
+Und insoweit berichten uns die Länder sehr frühzeitig.
+Wir berichten den Ländern aufgrund unserer Erkenntnisse.
+Und ich glaube, das ist auch das Entscheidende.
+Geuther: Es wurde einzelnen Ländern – gerade auch im Osten der Republik – vorgeworfen, eine Tat später als rechtsextremistisch einzuordnen als andere – vorsichtig gesagt.
+Stimmt das?
+Und wenn ja, stimmt das immer noch?
+Frank: Um hier eine Sensibilisierung auch bei jedem zu erreichen, haben wir, hat die Bundesanwaltschaft, in Zusammenarbeit aber auch mit den Generalstaatsanwaltschaften der Länder verschiedene Instrumentarien entwickelt.
+Eines ist zum Beispiel – auch, wenn das vielleicht banal klingen mag – die Entwicklung eines Formblattes, wie man frühzeitig rechtsextremistische Straftaten erkennen kann.
+Denn vielfach ist ein erster Kontakt mit rechtsextremistischen Straftaten nicht immer dann gegeben, wenn Volksverhetzungen begangen wurden, der Hitler-Gruß gezeigt wird, wenn Hakenkreuze an die Wand gemalt werden.
+Häufig sind es Straftaten der Allgemeinkriminalität.
+Es sind Körperverletzungshandlungen.
+Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
+Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
+Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
+Wie gehen Sie als Generalbundesanwalt damit um?
+Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
+In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
+Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
+Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
+Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
+Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
+Oder hat sich da eine größere Vernetzungsstruktur gebildet?
+Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
+Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
+Wir haben im Blick besonders: rechtsextremistische Gefährder.
+Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
+Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
+Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
+Das ist für uns sehr wichtig.
+Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
+Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
+Und man könnte auch weitergehen.
+Die Verrohung steigt offenbar insgesamt.
+Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
+Was kann Recht da überhaupt leisten?
+Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
+Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
+Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
+Seit Jahren steigt der Anteil von Gewaltstraftaten.
+Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
+Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
+Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
+Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
+Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
+Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frank: Ja.
+Zunächst möchte ich vielleicht eines vorweg sagen.
+Flüchtling ist oder einen anderen Aufenthaltstitel hat.
+Wir gehen diesen Hinweisen im Einzelnen nach.
+Da gibt es eine Reihe von Hinweisen, die sich als nichtzutreffend herausgestellt haben.
+Aber immer dann, wenn sich der Verdacht ergibt, ein begründeter Verdacht ergibt,  in einem doch fernab  gelegenen Kriegsgebiet – in dem ja jegliche staatliche Kontrolle, jede jegliche staatliche Struktur zusammengebrochen ist – auch Beweise zu erheben.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,13 +514,6 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -871,7 +840,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -888,9 +857,9 @@
     <col min="1" max="1" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="364" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -900,6 +869,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C43EA22B-6B0F-465F-89B1-D971C92024DC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -912,37 +900,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/new/260718.xlsx
+++ b/new/260718.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88270C11-222C-4636-8881-B161E12A26C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E3EBD-23B5-4957-B8DE-9D4D30D6A313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8600" yWindow="2380" windowWidth="16150" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9260" yWindow="4110" windowWidth="16150" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>每周采访-160731-Generalbundesanwalt</t>
   </si>
@@ -42,130 +43,6 @@
   </si>
   <si>
     <t>每周采访-160828-Frod</t>
-  </si>
-  <si>
-    <t>Jeder versteht, wenn die EU mit bestimmten Ländern auf der Welt Verträge abschließt über Freihandel, dass das überwiegend in deren Interesse ist, weil die auch Vorkehrungen bekommen, die es dann kapitalkräftigen Investoren aus Europa und den USA als ein geordnetes Wagnis erscheinen lassen, dort zu investieren.
-Aber die Fragen sind natürlich anders, wenn es um die Beziehung zwischen den großen Ländern gibt, die ähnliche Rechtssysteme haben.
-Und deshalb wundert mich die Debatte nicht – sie muss geführt werden.
-Detjen: Jetzt schauen wir mal rein auf den Teil der Investitionen, die Sie ansprechen.
-Würde Hamburg, was internationale, was amerikanische Investitionen angeht, von TTIP profitieren?
-Scholz: Wie gesagt, das Abkommen existiert nicht.
-Sie selber haben eben gesagt, man weiß gar nicht, ob es in der Präsidentschaft Obama noch was werden kann.
-Die Verhandlungen sind sehr weit zurückliegend.
-Der Zeitplan ist bisher, soweit ich das beurteilen kann, nicht eingehalten.
-Da muss man schon sehr skeptisch sein.
-Und wenn man hört, was im amerikanischen Wahlkampf so alles gesagt wird von den beiden Bewerbern um die Präsidentschaft – Hillary Clinton und Donald Trump –, dann ist da noch weiterer Zweifel angebracht.
-Ich will also nicht etwas beurteilen, was ich gar nicht kenne.
-Detjen: Das Deutschlandfunk-Interview dieser Woche, mit dem Ersten Bürgermeister von Hamburg, mit Olaf Scholz.
-Herr Bürgermeister, der Vorsitzende der SPD, Sigmar Gabriel, hat schwierige Zeiten in der Partei, jetzt steht er öffentlich auch noch wegen der Fusion Edeka/Tengelmann in der Kritik.
-In der Sache – das haben Sie immer deutlich gemacht – stehen Sie hinter ihm, Sie halten diese Fusion für richtig.
-Sind Sie sicher, dass Gabriel auch im schwierigen, heiklen Verfahren, um das es jetzt geht, alles richtiggemacht hat?
-Scholz: Ich kenne die Akten nicht, aber ich bin sehr überzeugt davon, dass das alles richtig gemacht worden ist, was dort in dem Wirtschaftsministerium vorbereitet worden ist und was an Diskussionen stattgefunden hat.
-Immerhin ist es ja so, dass hier ganz bewusst vorgesehen ist, dass es ein geordnetes Verfahren gibt und dann noch eine politische Möglichkeit, eine Fusion zu erlauben aus politischen Erwägungen heraus, zum Beispiel, weil man Arbeitsplätze sichern möchte.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hier geht es um Männer und Frauen, die sich Sorgen machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Ist das für die SPD auch eine Chance, mal wieder den Schulterschluss mit den Gewerkschaften im Kampf um Arbeitsplätze zu demonstrieren?
-Scholz: Man sollte solche Entscheidungen nicht unter solchen politischen Kriterien fällen – also, was nützt meiner Partei –, sondern hier geht es um viele Männer und Frauen, die in den Unternehmen arbeiten und die sich Sorgen um ihre Zukunft machen.
-Detjen: Ich habe das gefragt, weil sich der Bundeswirtschaftsminister mit dieser Entscheidung ja gegen die Empfehlung beziehungsweise Entscheidung derer hinweggesetzt hat, die für den freien Wettbewerb zuständig sind – Bundeskartellamt, Monopolkommission –, die eine andere Entscheidung empfohlen oder nahegelegt haben.
-Scholz: Er ist nicht der Erste, der das tut.
-Minister, die dieses Amt vor ihm hatten, aller Parteien, haben schon solche Genehmigungen erteilt.
-Und es wird auch nicht die letzte sein.
-Detjen: Herr Bürgermeister, wir stehen gut ein Jahr vor der Bundestagswahl.
-Das könnte die Zeit sein, eine vorläufige Bilanz der Großen Koalition zu ziehen, mit der sich Ihre Partei, die SPD, am Anfang ja schwergetan hat.
-Wie ist Ihre Bilanz ein Jahr vor der Bundestagswahl?
-Scholz: Wir haben viele Erfolge durchsetzen können.
-Der wichtigste ist sicherlich die Einführung eines allgemeinen, gleichen, flächendeckenden Mindestlohns in Deutschland.
-Deutschland ist Nachzügler.
-Das gibt es in vielen, vielen vergleichbaren Ländern – jetzt haben wir das auch.
-Und es gibt Verbesserungen etwa im Bereich der Sicherheit von Arbeitsplätzen und von Arbeitnehmerrechten, bei der Leiharbeit, bei Werkverträgen sind wir an der Sache dran.
-Das ist alles wichtig und eine gute Leistungsbilanz.
-Detjen: Das sah ja schon am Anfang dieser Großen Koalition so aus.
-In den ersten Monaten hat die SPD ein Projekt nach dem anderen durchgekriegt.
-Es wirkte so – so haben auch wir in den Medien das beschrieben –, als diktiert die SPD die Agenda dieser Großen Koalition.
-Das flachte dann etwas ab und vor allen Dingen hat es sich in den Umfragewerten nie richtig niedergeschlagen.
-Woran liegt das?
-Scholz: Erstmal ist es wichtig, dass man gute Arbeit leistet und es ist nicht schlecht, dass alle das immerhin attestieren.
-Das ist ja eine gute Empfehlung, wenn es zu Wahlen geht.
-Und im Übrigen geht es bei Wahlen darum, dass wir die Bürgerinnen und Bürger davon überzeugen, dass man uns auch das Mandat, die Regierung zuführen, anvertrauen kann.
-Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
-Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
-Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, Torsten Albig, der Ministerpräsident von Schleswig-Holstein, noch in Frage gestellt, ob die SPD 2017 überhaupt einen eigenen Kanzlerkandidaten aufstellen sollte.
-Das war vor der Flüchtlingskrise.
-Wie sieht das heute aus?
-Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
-Wir wollen den Kanzler dieser Republik stellen.
-Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
-"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Und Sie, das haben Sie immer wieder erklärt, sind dafür, dass Sigmar Gabriel das sein soll?
-Scholz: Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat, sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
-Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
-Scholz: Das ist ja nichts Schlechtes, dass man das allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
-Trotzdem gilt, der Parteivorsitzende wird einen Vorschlag machen.
-Und ich wiederhole es nochmal: Ein Parteivorsitzender ist immer ein guter Kandidat.
-Detjen: Wo ist die Linkspartei zurzeit für Sie ein Regierungspartner der SPD, ein guter Regierungspartner?
-wo in den Ländern?
-Auf Bundesebene auch?
-Scholz: Die Partei Die Linke vertritt politische Positionen im Hinblick auf die Entwicklung unseres Landes, auf die Entwicklung Europas, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
-Deshalb kann man beim Blick auf die Partei Die Linke große Skepsis haben, dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
-Ich halte das nicht für möglich.
-Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
-Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
-Ist das für Sie erstrebenswert?
-Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
-Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
-Und das sollte auch im Vordergrund der Bemühungen stehen.
-Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
-Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
-Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
-Scholz: Das glaube ich schon.
-Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
-Was ist da schiefgelaufen?
-Scholz: Weiß ich nicht.
-Ich kenne mich vor Ort nicht genug aus.
-Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
-Und das muss jetzt auch schnell in Ordnung gebracht werden.
-Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
-Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
-Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-Scholz: Letzteres ganz bestimmt nicht.
-Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
-Das kann ich mir auch nicht so richtig erklären.
-Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
-Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD. """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Dafür sorgen, dass es eine gute Zukunft gibt"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Warum ist die für Sie die """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Partei der schlechten Laune"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
-Und über sowas muss man diskutieren.
-Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
-Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>um hier dann eben Mobilitätsdienstleistungen anbieten zu können.
@@ -495,6 +372,126 @@
 Wir gehen diesen Hinweisen im Einzelnen nach.
 Da gibt es eine Reihe von Hinweisen, die sich als nichtzutreffend herausgestellt haben.
 Aber immer dann, wenn sich der Verdacht ergibt, ein begründeter Verdacht ergibt,  in einem doch fernab  gelegenen Kriegsgebiet – in dem ja jegliche staatliche Kontrolle, jede jegliche staatliche Struktur zusammengebrochen ist – auch Beweise zu erheben.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>In der Sache – das haben Sie immer deutlich gemacht – stehen Sie hinter ihm, Sie halten diese Fusion für richtig.
+Sind Sie sicher, dass Gabriel auch im schwierigen, heiklen Verfahren, um das es jetzt geht, alles richtiggemacht hat?
+Scholz: Ich kenne die Akten nicht, aber ich bin sehr überzeugt davon, dass das alles richtig gemacht worden ist, was dort in dem Wirtschaftsministerium vorbereitet worden ist und was an Diskussionen stattgefunden hat.
+Immerhin ist es ja so, dass hier ganz bewusst vorgesehen ist, dass es ein geordnetes Verfahren gibt und dann noch eine politische Möglichkeit, eine Fusion zu erlauben aus politischen Erwägungen heraus, zum Beispiel, weil man Arbeitsplätze sichern möchte.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Hier geht es um Männer und Frauen, die sich Sorgen machen"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Ist das für die SPD auch eine Chance, mal wieder den Schulterschluss mit den Gewerkschaften im Kampf um Arbeitsplätze zu demonstrieren?
+Scholz: Man sollte solche Entscheidungen nicht unter solchen politischen Kriterien fällen – also, was nützt meiner Partei –, sondern hier geht es um viele Männer und Frauen, die in den Unternehmen arbeiten und die sich Sorgen um ihre Zukunft machen.
+Detjen: Ich habe das gefragt, weil sich der Bundeswirtschaftsminister mit dieser Entscheidung ja gegen die Empfehlung beziehungsweise Entscheidung derer hinweggesetzt hat, die für den freien Wettbewerb zuständig sind – Bundeskartellamt, Monopolkommission –, die eine andere Entscheidung empfohlen oder nahegelegt haben.
+Scholz: Er ist nicht der Erste, der das tut.
+Minister, die dieses Amt vor ihm hatten, aller Parteien, haben schon solche Genehmigungen erteilt.
+Und es wird auch nicht die letzte sein.
+Detjen: Herr Bürgermeister, wir stehen gut ein Jahr vor der Bundestagswahl.
+Das könnte die Zeit sein, eine vorläufige Bilanz der Großen Koalition zu ziehen, mit der sich Ihre Partei, die SPD, am Anfang ja schwergetan hat.
+Wie ist Ihre Bilanz ein Jahr vor der Bundestagswahl?
+Scholz: Wir haben viele Erfolge durchsetzen können.
+Der wichtigste ist sicherlich die Einführung eines allgemeinen, gleichen, flächendeckenden Mindestlohns in Deutschland.
+Deutschland ist Nachzügler.
+Das gibt es in vielen, vielen vergleichbaren Ländern – jetzt haben wir das auch.
+Und es gibt Verbesserungen etwa im Bereich der Sicherheit von Arbeitsplätzen und von Arbeitnehmerrechten, bei der Leiharbeit, bei Werkverträgen sind wir an der Sache dran.
+Das ist alles wichtig und eine gute Leistungsbilanz.
+Detjen: Das sah ja schon am Anfang dieser Großen Koalition so aus.
+In den ersten Monaten hat die SPD ein Projekt nach dem anderen durchgekriegt.
+Es wirkte so – so haben auch wir in den Medien das beschrieben –, als diktiert die SPD die Agenda dieser Großen Koalition.
+Das flachte dann etwas ab und vor allen Dingen hat es sich in den Umfragewerten nie richtig niedergeschlagen.
+Woran liegt das?
+Scholz: Erstmal ist es wichtig, dass man gute Arbeit leistet und es ist nicht schlecht, dass alle das immerhin attestieren.
+Das ist ja eine gute Empfehlung, wenn es zu Wahlen geht.
+Und im Übrigen geht es bei Wahlen darum, dass wir die Bürgerinnen und Bürger davon überzeugen, dass man uns auch das Mandat, die Regierung zuführen, anvertrauen kann.
+Dann gibt das auch mehr Stimmen und mehr Prozentpunkte als in den gegenwärtigen Umfragen.
+Detjen: Ob man eine Regierung führen will, das war ja auch in Ihrer Partei gar nicht so unumstritten oder so gar nicht fraglos.
+Vor einem Jahr hat sozusagen Ihr Nachbar als Regierungschef, Torsten Albig, der Ministerpräsident von Schleswig-Holstein, noch in Frage gestellt, ob die SPD 2017 überhaupt einen eigenen Kanzlerkandidaten aufstellen sollte.
+Das war vor der Flüchtlingskrise.
+Wie sieht das heute aus?
+Scholz: Wir sind uns alle einig: Wir werden einen Kanzlerkandidaten aufstellen.
+Wir wollen den Kanzler dieser Republik stellen.
+Und Anfang des nächsten Jahres wird der Parteivorsitzende dazu einen Vorschlag machen.
+"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Und Sie, das haben Sie immer wieder erklärt, sind dafür, dass Sigmar Gabriel das sein soll?
+Scholz: Ein Parteivorsitzender ist immer ein guter Kanzlerkandidat, sonst wäre er übrigens auch ein schlechter Parteivorsitzender.
+Detjen: Und Sie gehören selbst zu den Mehreren, auf die Sigmar Gabriel auch immer wieder gezeigt hat, die in der SPD noch mögliche Kanzlerkanditen wären.
+Scholz: Das ist ja nichts Schlechtes, dass man das allgemein mehreren Männern und Frauen in der Führung der deutschen Sozialdemokratie zutraut.
+Trotzdem gilt, der Parteivorsitzende wird einen Vorschlag machen.
+Und ich wiederhole es nochmal: Ein Parteivorsitzender ist immer ein guter Kandidat.
+Detjen: Wo ist die Linkspartei zurzeit für Sie ein Regierungspartner der SPD, ein guter Regierungspartner?
+wo in den Ländern?
+Auf Bundesebene auch?
+Scholz: Die Partei Die Linke vertritt politische Positionen im Hinblick auf die Entwicklung unseres Landes, auf die Entwicklung Europas, auf globale Themen, mit denen man sich gegenwärtig nicht vorstellen kann, wie da eine gemeinsame Regierung funktionieren sollte.
+Deshalb kann man beim Blick auf die Partei Die Linke große Skepsis haben, dass die in der nächsten Zeit noch die Wende schaffen, dass sie regierungsgeeignet in einem deutschen Staat sind.
+Ich halte das nicht für möglich.
+Detjen: Das bezieht sich jetzt auf Koalitionen auf Bundesebene, was Regierung angeht.
+Vor der Bundestagswahl, vor der Bildung einer Bundesregierung steht die Wahl eines Bundespräsidenten, eine sozusagen rot-rot-grüne Koalition in der Bundesversammlung.
+Ist das für Sie erstrebenswert?
+Scholz: Ich wünsche mir, dass jemand Präsident oder Präsidentin wird, von dem die Bürgerinnen und Bürger sagen: Das ist ein guter Präsident, das ist eine gute Präsidentin.
+Da geht es nicht zu allererst um Parteipolitik, sondern darum, dass das Land zusammengehalten wird.
+Und das sollte auch im Vordergrund der Bemühungen stehen.
+Ich fände es auch sehr gut möglich, dass sich Parteien der jetzigen Regierung auf einen gemeinsamen Kandidaten verständigen, den auch die Grünen zum Beispiel und andere gut finden.
+Detjen: Herr Scholz, jetzt beginnt für die Parteien, zunächst mal als Vorbereitung auf die Wahl, die Aufstellung der Kandidatenlisten – das betrifft auch die SPD in Hamburg natürlich.
+Können Sie gewährleisten, dass die SPD in Hamburg keine Kandidatinnen oder Kandidaten aufstellt, die dann danach mit gefälschten Lebensläufen den Bürgern etwas vormachen?
+Scholz: Das glaube ich schon.
+Detjen: Das war in Nordrhein-Westfalen offenbar nicht so einfach.
+Was ist da schiefgelaufen?
+Scholz: Weiß ich nicht.
+Ich kenne mich vor Ort nicht genug aus.
+Ich glaube, dass alle sehr betrübt darüber sind, dass es so ist.
+Und das muss jetzt auch schnell in Ordnung gebracht werden.
+Detjen: Zu den Befunden in dieser Affäre um die SPD-Bundestagsabgeordnete Petra Hinz gehört ja auch das Bild, dass da eine SPD-Abgeordnete war, die eigentlich niemand richtig kannte.
+Der Vorsitzende des SPD-Unterbezirks Essen, der nordrhein-westfälische Justizminister Kutschaty sagt, es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
+Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
+Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
+Scholz: Letzteres ganz bestimmt nicht.
+Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
+Das kann ich mir auch nicht so richtig erklären.
+Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
+Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
+Das bezog sich nicht auf die SPD, richtig?
+Scholz: Klar, das bezog sich auf die AfD. """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Dafür sorgen, dass es eine gute Zukunft gibt"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Detjen: Warum ist die für Sie die """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Partei der schlechten Laune"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
+Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
+Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
+Was machen wir mit unseren öffentlichen Haushalten?
+Wie statten wir die Bundeswehr und unsere Polizei gut aus?
+Was machen wir, um die Bildung zu verbessern an den Schulen?
+Wie setzen wir Forschung und Universitäten auf die richtige Spur?
+Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
+Und über sowas muss man diskutieren.
+Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
+Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
+Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
+Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
+Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
+Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
+Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
+Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
+Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
+Das muss das Ergebnis des letzten Jahres sein.
+Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
+Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
+Detjen: Nochmal der Blick konkret auf Hamburg.
+Was haben Sie geschafft in diesem Jahr?
+Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
+'.
+Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
+Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
+Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
+Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
+Detjen: Und vieles ist noch zu tun.
+Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen: """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Wir schaffen das"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" ?
+Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
+Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
+Detjen: Herr Bürgermeister, vielen Dank.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ein geordnetes Wagnis erscheinen lassen, dort zu investieren.
+Und deshalb wundert mich die Debatte nicht – sie muss geführt werden.
+Detjen: Jetzt schauen wir mal rein auf den Teil der Investitionen, die Sie ansprechen.
+Scholz: Wie gesagt, das Abkommen existiert nicht.
+Sie selber haben eben gesagt, man weiß gar nicht, ob es in der Präsidentschaft Obama noch was werden kann.
+Die Verhandlungen sind sehr weit zurückliegend.
+Der Zeitplan ist bisher, soweit ich das beurteilen kann, nicht eingehalten.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -840,7 +837,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +856,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -878,7 +875,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -888,6 +885,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD29598D-36FB-4A4C-8449-76AF04712427}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="224" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -917,16 +933,16 @@
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
